--- a/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
+++ b/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54105F9-699E-40C1-91E9-7B98EAFB177C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C43B9EE-BEE0-BB49-8E61-51C4620CFE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="511">
   <si>
     <t>Name</t>
   </si>
@@ -419,9 +419,6 @@
   </si>
   <si>
     <t>microfiltration_zo</t>
-  </si>
-  <si>
-    <t>microscreen filtration</t>
   </si>
   <si>
     <t>microscreen_filtration_zo</t>
@@ -1655,9 +1652,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1695,9 +1692,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1730,26 +1727,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1782,26 +1762,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1975,21 +1938,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J92"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J91"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.46484375" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
     <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="10.53125" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.19921875" customWidth="1"/>
-    <col min="8" max="8" width="38.53125" customWidth="1"/>
-    <col min="9" max="9" width="30.19921875" customWidth="1"/>
-    <col min="10" max="10" width="25.53125" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" customWidth="1"/>
+    <col min="8" max="8" width="38.5" customWidth="1"/>
+    <col min="9" max="9" width="30.1640625" customWidth="1"/>
+    <col min="10" max="10" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1997,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -2006,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -2021,7 +1984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2029,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2056,7 +2019,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2064,7 +2027,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2091,15 +2054,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2126,15 +2089,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B5" t="s">
         <v>463</v>
       </c>
-      <c r="B5" t="s">
-        <v>464</v>
-      </c>
       <c r="C5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -2160,7 +2123,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2168,7 +2131,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D6" t="s">
         <v>30</v>
@@ -2183,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="1"/>
@@ -2194,15 +2157,15 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -2217,7 +2180,7 @@
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="1"/>
@@ -2228,7 +2191,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2236,7 +2199,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -2263,7 +2226,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -2271,7 +2234,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -2298,7 +2261,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2306,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -2333,15 +2296,15 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -2368,7 +2331,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2376,7 +2339,7 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D12" t="s">
         <v>30</v>
@@ -2402,7 +2365,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -2410,7 +2373,7 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -2437,7 +2400,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2445,7 +2408,7 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D14" t="s">
         <v>30</v>
@@ -2471,7 +2434,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -2479,7 +2442,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -2506,15 +2469,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>466</v>
+      </c>
+      <c r="B16" t="s">
         <v>467</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>468</v>
-      </c>
-      <c r="C16" t="s">
-        <v>469</v>
       </c>
       <c r="D16" t="s">
         <v>30</v>
@@ -2529,7 +2492,7 @@
         <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="1"/>
@@ -2540,7 +2503,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2548,7 +2511,7 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D17" t="s">
         <v>30</v>
@@ -2574,7 +2537,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -2582,7 +2545,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D18" t="s">
         <v>30</v>
@@ -2608,7 +2571,7 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -2616,7 +2579,7 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -2643,15 +2606,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>470</v>
+      </c>
+      <c r="B20" t="s">
         <v>471</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>472</v>
-      </c>
-      <c r="C20" t="s">
-        <v>473</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -2677,7 +2640,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2685,7 +2648,7 @@
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -2712,7 +2675,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2720,7 +2683,7 @@
         <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D22" t="s">
         <v>30</v>
@@ -2746,7 +2709,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2754,7 +2717,7 @@
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D23" t="s">
         <v>30</v>
@@ -2769,7 +2732,7 @@
         <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="1"/>
@@ -2780,7 +2743,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2788,7 +2751,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D24" t="s">
         <v>30</v>
@@ -2803,7 +2766,7 @@
         <v>58</v>
       </c>
       <c r="H24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="1"/>
@@ -2814,7 +2777,7 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2822,7 +2785,7 @@
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -2849,7 +2812,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2857,7 +2820,7 @@
         <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2884,7 +2847,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -2892,7 +2855,7 @@
         <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D27" t="s">
         <v>30</v>
@@ -2918,7 +2881,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2926,7 +2889,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2953,7 +2916,7 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2961,7 +2924,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D29" t="s">
         <v>30</v>
@@ -2987,7 +2950,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -2995,7 +2958,7 @@
         <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -3022,7 +2985,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -3030,7 +2993,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D31" t="s">
         <v>57</v>
@@ -3056,7 +3019,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -3064,7 +3027,7 @@
         <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -3091,7 +3054,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -3099,7 +3062,7 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D33" t="s">
         <v>30</v>
@@ -3125,15 +3088,15 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>507</v>
+      </c>
+      <c r="B34" t="s">
         <v>508</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>509</v>
-      </c>
-      <c r="C34" t="s">
-        <v>510</v>
       </c>
       <c r="D34" t="s">
         <v>30</v>
@@ -3148,7 +3111,7 @@
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="1"/>
@@ -3159,7 +3122,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -3167,7 +3130,7 @@
         <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D35" t="s">
         <v>30</v>
@@ -3193,7 +3156,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -3201,7 +3164,7 @@
         <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -3228,7 +3191,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -3236,7 +3199,7 @@
         <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D37" t="s">
         <v>30</v>
@@ -3262,7 +3225,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -3270,7 +3233,7 @@
         <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -3297,7 +3260,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3305,7 +3268,7 @@
         <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D39" t="s">
         <v>92</v>
@@ -3330,7 +3293,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -3338,7 +3301,7 @@
         <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D40" t="s">
         <v>30</v>
@@ -3364,7 +3327,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -3372,7 +3335,7 @@
         <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D41" t="s">
         <v>30</v>
@@ -3398,7 +3361,7 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>100</v>
       </c>
@@ -3406,7 +3369,7 @@
         <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D42" t="s">
         <v>30</v>
@@ -3421,7 +3384,7 @@
         <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I42" t="str">
         <f t="shared" si="3"/>
@@ -3432,7 +3395,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -3440,7 +3403,7 @@
         <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D43" t="s">
         <v>30</v>
@@ -3466,15 +3429,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>474</v>
+      </c>
+      <c r="B44" t="s">
+        <v>473</v>
+      </c>
+      <c r="C44" t="s">
         <v>475</v>
-      </c>
-      <c r="B44" t="s">
-        <v>474</v>
-      </c>
-      <c r="C44" t="s">
-        <v>476</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -3489,7 +3452,7 @@
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I44" t="str">
         <f t="shared" si="3"/>
@@ -3500,15 +3463,15 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D45" t="s">
         <v>30</v>
@@ -3523,7 +3486,7 @@
         <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I45" t="str">
         <f t="shared" si="3"/>
@@ -3534,7 +3497,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -3542,7 +3505,7 @@
         <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -3561,15 +3524,15 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" ref="I46:I92" si="5">IF(E46="SIDO","single-input, double-output",IF(E46="SISO","single-input, single-output",IF(E46="PT","pass-through",IF(E46="DISO","double-input, single-output",IF(E46="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <f t="shared" ref="I46:I91" si="5">IF(E46="SIDO","single-input, double-output",IF(E46="SISO","single-input, single-output",IF(E46="PT","pass-through",IF(E46="DISO","double-input, single-output",IF(E46="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
         <v>pass-through</v>
       </c>
       <c r="J46" t="str">
-        <f t="shared" ref="J46:J92" si="6">IF(E46="SIDO","sido_methods",IF(E46="SISO","siso_methods",IF(E46="PT","pt_methods",IF(E46="DISO","diso_methods",IF(E46="SIDO reactive","sidor_methods","")))))</f>
+        <f t="shared" ref="J46:J91" si="6">IF(E46="SIDO","sido_methods",IF(E46="SISO","siso_methods",IF(E46="PT","pt_methods",IF(E46="DISO","diso_methods",IF(E46="SIDO reactive","sidor_methods","")))))</f>
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>106</v>
       </c>
@@ -3577,7 +3540,7 @@
         <v>107</v>
       </c>
       <c r="C47" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -3604,7 +3567,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>108</v>
       </c>
@@ -3612,7 +3575,7 @@
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D48" t="s">
         <v>30</v>
@@ -3638,7 +3601,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>111</v>
       </c>
@@ -3646,7 +3609,7 @@
         <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D49" t="s">
         <v>30</v>
@@ -3672,7 +3635,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -3680,7 +3643,7 @@
         <v>115</v>
       </c>
       <c r="C50" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -3706,7 +3669,7 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -3714,7 +3677,7 @@
         <v>118</v>
       </c>
       <c r="C51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D51" t="s">
         <v>30</v>
@@ -3740,15 +3703,15 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>479</v>
+      </c>
+      <c r="B52" t="s">
         <v>480</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>481</v>
-      </c>
-      <c r="C52" t="s">
-        <v>482</v>
       </c>
       <c r="D52" t="s">
         <v>30</v>
@@ -3763,7 +3726,7 @@
         <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I52" t="str">
         <f t="shared" si="5"/>
@@ -3774,7 +3737,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>120</v>
       </c>
@@ -3782,7 +3745,7 @@
         <v>121</v>
       </c>
       <c r="C53" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -3809,7 +3772,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>122</v>
       </c>
@@ -3817,7 +3780,7 @@
         <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -3844,15 +3807,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>483</v>
+      </c>
+      <c r="B55" t="s">
         <v>484</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>485</v>
-      </c>
-      <c r="C55" t="s">
-        <v>486</v>
       </c>
       <c r="D55" t="s">
         <v>30</v>
@@ -3867,7 +3830,7 @@
         <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="5"/>
@@ -3878,7 +3841,7 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -3886,7 +3849,7 @@
         <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D56" t="s">
         <v>30</v>
@@ -3912,15 +3875,15 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>487</v>
+      </c>
+      <c r="B57" t="s">
         <v>488</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>489</v>
-      </c>
-      <c r="C57" t="s">
-        <v>490</v>
       </c>
       <c r="D57" t="s">
         <v>30</v>
@@ -3935,7 +3898,7 @@
         <v>12</v>
       </c>
       <c r="H57" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="5"/>
@@ -3946,7 +3909,7 @@
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3954,7 +3917,7 @@
         <v>128</v>
       </c>
       <c r="C58" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -3981,50 +3944,49 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" t="str">
-        <f>IF(D59="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
+        <v>65</v>
       </c>
       <c r="I59" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J59" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -4036,10 +3998,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" t="s">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="H60" t="str">
+        <f>IF(D60="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I60" t="str">
         <f t="shared" si="5"/>
@@ -4050,56 +4013,55 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C61" t="s">
         <v>405</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
-      </c>
-      <c r="H61" t="str">
-        <f>IF(D61="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H61" t="s">
+        <v>136</v>
       </c>
       <c r="I61" t="str">
         <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J61" t="str">
         <f t="shared" si="6"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="D62" t="s">
         <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -4108,26 +4070,26 @@
         <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I62" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J62" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+        <v>siso_methods</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>370</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D63" t="s">
         <v>30</v>
@@ -4142,7 +4104,7 @@
         <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I63" t="str">
         <f t="shared" si="5"/>
@@ -4153,98 +4115,99 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>492</v>
       </c>
       <c r="C64" t="s">
-        <v>425</v>
+        <v>493</v>
       </c>
       <c r="D64" t="s">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>142</v>
+        <v>494</v>
       </c>
       <c r="I64" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, single-output</v>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J64" t="str">
         <f t="shared" si="6"/>
-        <v>siso_methods</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>492</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>493</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="D65" t="s">
         <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>495</v>
+        <v>144</v>
       </c>
       <c r="I65" t="str">
         <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J65" t="str">
         <f t="shared" si="6"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C66" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>31</v>
-      </c>
-      <c r="H66" t="s">
-        <v>145</v>
+        <v>12</v>
+      </c>
+      <c r="H66" t="str">
+        <f>IF(D66="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I66" t="str">
         <f t="shared" si="5"/>
@@ -4255,65 +4218,65 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
-      </c>
-      <c r="H67" t="str">
-        <f>IF(D67="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H67" t="s">
+        <v>149</v>
       </c>
       <c r="I67" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J67" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C68" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
-      </c>
-      <c r="H68" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="H68" t="str">
+        <f>IF(D68="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I68" t="str">
         <f t="shared" si="5"/>
@@ -4324,12 +4287,12 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s">
         <v>409</v>
@@ -4338,7 +4301,7 @@
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -4352,25 +4315,25 @@
       </c>
       <c r="I69" t="str">
         <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J69" t="str">
         <f t="shared" si="6"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
@@ -4381,9 +4344,8 @@
       <c r="G70" t="s">
         <v>12</v>
       </c>
-      <c r="H70" t="str">
-        <f>IF(D70="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H70" t="s">
+        <v>65</v>
       </c>
       <c r="I70" t="str">
         <f t="shared" si="5"/>
@@ -4394,18 +4356,18 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
@@ -4417,7 +4379,7 @@
         <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="5"/>
@@ -4428,18 +4390,18 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
         <v>411</v>
       </c>
       <c r="D72" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
@@ -4450,8 +4412,9 @@
       <c r="G72" t="s">
         <v>12</v>
       </c>
-      <c r="H72" t="s">
-        <v>159</v>
+      <c r="H72" t="str">
+        <f>IF(D72="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I72" t="str">
         <f t="shared" si="5"/>
@@ -4462,15 +4425,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
@@ -4497,21 +4460,21 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="D74" t="s">
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -4525,22 +4488,22 @@
       </c>
       <c r="I74" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J74" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
@@ -4567,18 +4530,18 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -4589,9 +4552,8 @@
       <c r="G76" t="s">
         <v>12</v>
       </c>
-      <c r="H76" t="str">
-        <f>IF(D76="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H76" t="s">
+        <v>169</v>
       </c>
       <c r="I76" t="str">
         <f t="shared" si="5"/>
@@ -4602,18 +4564,18 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>168</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>496</v>
       </c>
       <c r="C77" t="s">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -4625,7 +4587,7 @@
         <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>170</v>
+        <v>498</v>
       </c>
       <c r="I77" t="str">
         <f t="shared" si="5"/>
@@ -4636,21 +4598,21 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C78" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -4659,41 +4621,41 @@
         <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="I78" t="str">
         <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J78" t="str">
         <f t="shared" si="6"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s">
-        <v>501</v>
+        <v>456</v>
       </c>
       <c r="C79" t="s">
-        <v>502</v>
+        <v>452</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H79" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I79" t="str">
         <f t="shared" si="5"/>
@@ -4704,52 +4666,52 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>504</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
-        <v>457</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D80" t="s">
         <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>505</v>
+        <v>172</v>
       </c>
       <c r="I80" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J80" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -4760,8 +4722,9 @@
       <c r="G81" t="s">
         <v>21</v>
       </c>
-      <c r="H81" t="s">
-        <v>173</v>
+      <c r="H81" t="str">
+        <f>IF(D81="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I81" t="str">
         <f t="shared" si="5"/>
@@ -4772,15 +4735,15 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
@@ -4792,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H82" t="str">
         <f>IF(D82="basic","cost_power_law_flow")</f>
@@ -4807,12 +4770,12 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
         <v>414</v>
@@ -4821,7 +4784,7 @@
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -4835,22 +4798,22 @@
       </c>
       <c r="I83" t="str">
         <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J83" t="str">
         <f t="shared" si="6"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
@@ -4877,21 +4840,21 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -4899,28 +4862,27 @@
       <c r="G85" t="s">
         <v>12</v>
       </c>
-      <c r="H85" t="str">
-        <f>IF(D85="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H85" t="s">
+        <v>183</v>
       </c>
       <c r="I85" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J85" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+        <v>siso_methods</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C86" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
         <v>30</v>
@@ -4935,7 +4897,7 @@
         <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I86" t="str">
         <f t="shared" si="5"/>
@@ -4946,21 +4908,21 @@
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -4969,29 +4931,29 @@
         <v>12</v>
       </c>
       <c r="H87" t="s">
-        <v>187</v>
+        <v>460</v>
       </c>
       <c r="I87" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, single-output</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J87" t="str">
         <f t="shared" si="6"/>
-        <v>siso_methods</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C88" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -5002,8 +4964,9 @@
       <c r="G88" t="s">
         <v>12</v>
       </c>
-      <c r="H88" t="s">
-        <v>461</v>
+      <c r="H88" t="str">
+        <f>IF(D88="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I88" t="str">
         <f t="shared" si="5"/>
@@ -5014,15 +4977,15 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
@@ -5049,47 +5012,46 @@
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" t="str">
-        <f>IF(D90="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H90" t="s">
+        <v>65</v>
       </c>
       <c r="I90" t="str">
         <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J90" t="str">
         <f t="shared" si="6"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C91" t="s">
         <v>439</v>
@@ -5101,13 +5063,13 @@
         <v>27</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H91" t="s">
-        <v>65</v>
+        <v>197</v>
       </c>
       <c r="I91" t="str">
         <f t="shared" si="5"/>
@@ -5118,43 +5080,9 @@
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>196</v>
-      </c>
-      <c r="B92" t="s">
-        <v>197</v>
-      </c>
-      <c r="C92" t="s">
-        <v>440</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>27</v>
-      </c>
-      <c r="F92" t="b">
-        <v>1</v>
-      </c>
-      <c r="G92" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" t="s">
-        <v>198</v>
-      </c>
-      <c r="I92" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J92" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J92">
-    <sortCondition ref="B2:B92"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J91">
+    <sortCondition ref="B2:B91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5164,576 +5092,576 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G77"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="33.53125" customWidth="1"/>
-    <col min="3" max="3" width="31.46484375" customWidth="1"/>
+    <col min="2" max="2" width="33.5" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" t="str">
         <f>CONCATENATE(A1,"_zo")</f>
         <v>aeration_basin_zo</v>
       </c>
       <c r="C1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" t="s">
         <v>200</v>
-      </c>
-      <c r="D1" t="s">
-        <v>201</v>
       </c>
       <c r="G1" t="str">
         <f>CONCATENATE(C1," ",D1)</f>
         <v>aeration basin</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B2" t="str">
         <f t="shared" ref="B2:B65" si="0">CONCATENATE(A2,"_zo")</f>
         <v>air_flotation_zo</v>
       </c>
       <c r="C2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" t="s">
         <v>203</v>
-      </c>
-      <c r="D2" t="s">
-        <v>204</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2:G65" si="1">CONCATENATE(C2," ",D2)</f>
         <v>air flotation</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B3" t="str">
         <f t="shared" si="0"/>
         <v>anaerobic_digestion_oxidation_zo</v>
       </c>
       <c r="C3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
         <v>206</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>207</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="str">
+        <f t="shared" si="1"/>
+        <v>anaerobic digestion</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" si="1"/>
-        <v>anaerobic digestion</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" si="0"/>
         <v>anaerobic_mbr_mec_zo</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" t="s">
         <v>210</v>
-      </c>
-      <c r="E4" t="s">
-        <v>211</v>
       </c>
       <c r="G4" t="str">
         <f>CONCATENATE(C4," ",D4," ",E4)</f>
         <v>anaerobic mbr mec</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
         <v>backwash_solids_handling_zo</v>
       </c>
       <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
         <v>213</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>214</v>
-      </c>
-      <c r="E5" t="s">
-        <v>215</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" ref="G5:G6" si="2">CONCATENATE(C5," ",D5," ",E5)</f>
         <v>backwash solids handling</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
         <v>bio_active_filtration_zo</v>
       </c>
       <c r="C6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" t="s">
         <v>217</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>218</v>
-      </c>
-      <c r="E6" t="s">
-        <v>219</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="2"/>
         <v>bio active filtration</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
         <v>bioreactor_zo</v>
       </c>
       <c r="C7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">bioreactor </v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">bioreactor </v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>blending_resevoir_zo</v>
       </c>
       <c r="C8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" t="s">
         <v>222</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>blending resevoir</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="1"/>
-        <v>blending resevoir</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>brine_concentrator_zo</v>
       </c>
       <c r="C9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" t="s">
         <v>225</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>brine concentrator</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="1"/>
-        <v>brine concentrator</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>buffer_tank_zo</v>
       </c>
       <c r="C10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" t="s">
         <v>228</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>buffer tank</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="1"/>
-        <v>buffer tank</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>CANDOP_zo</v>
       </c>
       <c r="C11" t="s">
+        <v>229</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">CANDOP </v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">CANDOP </v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>cartridge_filtration_zo</v>
       </c>
       <c r="C12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>cartridge filtration</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D12" t="s">
-        <v>219</v>
-      </c>
-      <c r="G12" t="str">
-        <f t="shared" si="1"/>
-        <v>cartridge filtration</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>chemical_addition_zo</v>
       </c>
       <c r="C13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" t="s">
         <v>234</v>
       </c>
-      <c r="D13" t="s">
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>chemical addition</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="G13" t="str">
-        <f t="shared" si="1"/>
-        <v>chemical addition</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>chlorination_zo</v>
       </c>
       <c r="C14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">chlorination </v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="G14" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">chlorination </v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>clarifier_zo</v>
       </c>
       <c r="C15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">clarifier </v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">clarifier </v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>co2_addition_zo</v>
       </c>
       <c r="C16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>co2 addition</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="D16" t="s">
-        <v>235</v>
-      </c>
-      <c r="G16" t="str">
-        <f t="shared" si="1"/>
-        <v>co2 addition</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>coag_and_floc_zo</v>
       </c>
       <c r="C17" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" t="s">
         <v>241</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>242</v>
-      </c>
-      <c r="E17" t="s">
-        <v>243</v>
       </c>
       <c r="G17" t="str">
         <f>CONCATENATE(C17," ",D17," ",E17)</f>
         <v>coag and floc</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>cofermentation_zo</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" ref="G18:G19" si="3">CONCATENATE(C18," ",D18," ",E18)</f>
         <v xml:space="preserve">cofermentation  </v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>constructed_wetlands_zo</v>
       </c>
       <c r="C19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" t="s">
         <v>246</v>
-      </c>
-      <c r="D19" t="s">
-        <v>247</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">constructed wetlands </v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>conventional_activated_sludge_zo</v>
       </c>
       <c r="C20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" t="s">
         <v>249</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>250</v>
-      </c>
-      <c r="E20" t="s">
-        <v>251</v>
       </c>
       <c r="G20" t="str">
         <f>CONCATENATE(C20," ",D20," ",E20)</f>
         <v>conventional activated sludge</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>cooling_supply_zo</v>
       </c>
       <c r="C21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" t="s">
         <v>253</v>
-      </c>
-      <c r="D21" t="s">
-        <v>254</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ref="G21:G22" si="4">CONCATENATE(C21," ",D21," ",E21)</f>
         <v xml:space="preserve">cooling supply </v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>cooling_tower_zo</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">cooling tower </v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>decarbonator_zo</v>
       </c>
       <c r="C23" t="s">
+        <v>256</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">decarbonator </v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">decarbonator </v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>deep_well_injection_zo</v>
       </c>
       <c r="C24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" t="s">
         <v>259</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>260</v>
-      </c>
-      <c r="E24" t="s">
-        <v>261</v>
       </c>
       <c r="G24" t="str">
         <f>CONCATENATE(C24," ",D24," ",E24)</f>
         <v>deep well injection</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>dissolved_air_flotation_zo</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" t="s">
         <v>203</v>
-      </c>
-      <c r="E25" t="s">
-        <v>204</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" ref="G25" si="5">CONCATENATE(C25," ",D25," ",E25)</f>
         <v>dissolved air flotation</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>dmbr_zo</v>
       </c>
       <c r="C26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G26" t="str">
         <f>CONCATENATE(C26," ",D26)</f>
         <v xml:space="preserve">dmbr </v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>dual_media_filtration_zo</v>
       </c>
       <c r="C27" t="s">
+        <v>265</v>
+      </c>
+      <c r="D27" t="s">
         <v>266</v>
       </c>
-      <c r="D27" t="s">
-        <v>267</v>
-      </c>
       <c r="E27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G27" t="str">
         <f>CONCATENATE(C27," ",D27," ",E27)</f>
         <v>dual media filtration</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>electrochemical_nutrient_removal_zo</v>
       </c>
       <c r="C28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
         <v>269</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>270</v>
-      </c>
-      <c r="E28" t="s">
-        <v>271</v>
       </c>
       <c r="G28" t="str">
         <f>CONCATENATE(C28," ",D28," ",E28)</f>
         <v>electrochemical nutrient removal</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>electrodialysis_reversal_zo</v>
       </c>
       <c r="C29" t="s">
+        <v>272</v>
+      </c>
+      <c r="D29" t="s">
         <v>273</v>
       </c>
-      <c r="D29" t="s">
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v>electrodialysis reversal</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="1"/>
-        <v>electrodialysis reversal</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
@@ -5743,477 +5671,477 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
+        <v>275</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v>energy recovery</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="1"/>
-        <v>energy recovery</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>evaporation_pond_zo</v>
       </c>
       <c r="C31" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" t="s">
         <v>278</v>
       </c>
-      <c r="D31" t="s">
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v>evaporation pond</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="G31" t="str">
-        <f t="shared" si="1"/>
-        <v>evaporation pond</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>feed_water_tank_zo</v>
       </c>
       <c r="C32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" t="s">
         <v>281</v>
       </c>
-      <c r="D32" t="s">
-        <v>282</v>
-      </c>
       <c r="E32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G32" t="str">
         <f>CONCATENATE(C32," ",D32," ",E32)</f>
         <v>feed water tank</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>feed_zo</v>
       </c>
       <c r="C33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">feed </v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>filter_press_zo</v>
       </c>
       <c r="C34" t="s">
+        <v>283</v>
+      </c>
+      <c r="D34" t="s">
         <v>284</v>
       </c>
-      <c r="D34" t="s">
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>filter press</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="G34" t="str">
-        <f t="shared" si="1"/>
-        <v>filter press</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>fixed_bed_zo</v>
       </c>
       <c r="C35" t="s">
+        <v>286</v>
+      </c>
+      <c r="D35" t="s">
         <v>287</v>
       </c>
-      <c r="D35" t="s">
+      <c r="G35" t="str">
+        <f t="shared" si="1"/>
+        <v>fixed bed</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="G35" t="str">
-        <f t="shared" si="1"/>
-        <v>fixed bed</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>gac_zo</v>
       </c>
       <c r="C36" t="s">
+        <v>288</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">gac </v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="G36" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">gac </v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>gas_sparged_membrane_zo</v>
       </c>
       <c r="C37" t="s">
+        <v>290</v>
+      </c>
+      <c r="D37" t="s">
         <v>291</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>292</v>
-      </c>
-      <c r="E37" t="s">
-        <v>293</v>
       </c>
       <c r="G37" t="str">
         <f>CONCATENATE(C37," ",D37," ",E37)</f>
         <v>gas sparged membrane</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>injection_well_disposal_zo</v>
       </c>
       <c r="C38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G38" t="str">
         <f>CONCATENATE(C38," ",D38," ",E38)</f>
         <v>injection well disposal</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>intrusion_mitigation_zo</v>
       </c>
       <c r="C39" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" t="s">
         <v>297</v>
       </c>
-      <c r="D39" t="s">
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
+        <v>intrusion mitigation</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="G39" t="str">
-        <f t="shared" si="1"/>
-        <v>intrusion mitigation</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>ion_exchange_zo</v>
       </c>
       <c r="C40" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" t="s">
         <v>300</v>
       </c>
-      <c r="D40" t="s">
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>ion exchange</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="G40" t="str">
-        <f t="shared" si="1"/>
-        <v>ion exchange</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>iron_and_manganese_removal_zo</v>
       </c>
       <c r="C41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" t="s">
         <v>303</v>
       </c>
-      <c r="D41" t="s">
-        <v>242</v>
-      </c>
-      <c r="E41" t="s">
-        <v>304</v>
-      </c>
       <c r="F41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G41" t="str">
         <f>CONCATENATE(C41," ",D41," ",E41," ",F41)</f>
         <v>iron and manganese removal</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>landfill_zo</v>
       </c>
       <c r="C42" t="s">
+        <v>304</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">landfill </v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="G42" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">landfill </v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>mabr_zo</v>
       </c>
       <c r="C43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">mabr </v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>mbr_zo</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">mbr </v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>media_filtration_zo</v>
       </c>
       <c r="C45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="1"/>
         <v>media filtration</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>metab_zo</v>
       </c>
       <c r="C46" t="s">
+        <v>307</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">metab </v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="G46" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">metab </v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>microfiltration_zo</v>
       </c>
       <c r="C47" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">microfiltration </v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="G47" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">microfiltration </v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>microscreen_filtration_zo</v>
       </c>
       <c r="C48" t="s">
+        <v>310</v>
+      </c>
+      <c r="D48" t="s">
+        <v>218</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="1"/>
+        <v>microscreen filtration</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="D48" t="s">
-        <v>219</v>
-      </c>
-      <c r="G48" t="str">
-        <f t="shared" si="1"/>
-        <v>microscreen filtration</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>municipal_drinking_zo</v>
       </c>
       <c r="C49" t="s">
+        <v>312</v>
+      </c>
+      <c r="D49" t="s">
         <v>313</v>
       </c>
-      <c r="D49" t="s">
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>municipal drinking</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="G49" t="str">
-        <f t="shared" si="1"/>
-        <v>municipal drinking</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>municipal_wwtp_zo</v>
       </c>
       <c r="C50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D50" t="s">
+        <v>315</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>municipal wwtp</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="G50" t="str">
-        <f t="shared" si="1"/>
-        <v>municipal wwtp</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>nanofiltration_zo</v>
       </c>
       <c r="C51" t="s">
+        <v>316</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">nanofiltration </v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="G51" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">nanofiltration </v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>ozone_aop _zo</v>
       </c>
       <c r="C52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D52" t="s">
         <v>319</v>
       </c>
-      <c r="D52" t="s">
-        <v>320</v>
-      </c>
       <c r="G52" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">ozone aop </v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>ozone_zo</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">ozone </v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="0"/>
         <v>photothermal_membrane_zo</v>
       </c>
       <c r="C54" t="s">
+        <v>321</v>
+      </c>
+      <c r="D54" t="s">
+        <v>292</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>photothermal membrane</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="D54" t="s">
-        <v>293</v>
-      </c>
-      <c r="G54" t="str">
-        <f t="shared" si="1"/>
-        <v>photothermal membrane</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="0"/>
         <v>primary_separator_zo</v>
       </c>
       <c r="C55" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" t="s">
         <v>324</v>
       </c>
-      <c r="D55" t="s">
-        <v>325</v>
-      </c>
       <c r="G55" t="str">
         <f t="shared" si="1"/>
         <v>primary separator</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
@@ -6222,409 +6150,409 @@
         <v>pump_electricity_zo</v>
       </c>
       <c r="C56" t="s">
+        <v>325</v>
+      </c>
+      <c r="D56" t="s">
         <v>326</v>
       </c>
-      <c r="D56" t="s">
-        <v>327</v>
-      </c>
       <c r="G56" t="str">
         <f t="shared" si="1"/>
         <v>pump electricity</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>pump_zo</v>
       </c>
       <c r="C57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">pump </v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>screen_zo</v>
       </c>
       <c r="C58" t="s">
+        <v>327</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">screen </v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="G58" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">screen </v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A59" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="0"/>
         <v>secondary_treatment_wwtp_zo</v>
       </c>
       <c r="C59" t="s">
+        <v>329</v>
+      </c>
+      <c r="D59" t="s">
         <v>330</v>
       </c>
-      <c r="D59" t="s">
-        <v>331</v>
-      </c>
       <c r="E59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G59" t="str">
         <f>CONCATENATE(C59," ",D59," ",E59)</f>
         <v>secondary treatment wwtp</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="0"/>
         <v>sedimentation_zo</v>
       </c>
       <c r="C60" t="s">
+        <v>331</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">sedimentation </v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="G60" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">sedimentation </v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="0"/>
         <v>settling_pond_zo</v>
       </c>
       <c r="C61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D61" t="s">
+        <v>278</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="1"/>
+        <v>settling pond</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D61" t="s">
-        <v>279</v>
-      </c>
-      <c r="G61" t="str">
-        <f t="shared" si="1"/>
-        <v>settling pond</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A62" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="0"/>
         <v>sludge_tank_zo</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="1"/>
         <v>sludge tank</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="0"/>
         <v>smp_zo</v>
       </c>
       <c r="C63" t="s">
+        <v>335</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">smp </v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="G63" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">smp </v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A64" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="0"/>
         <v>static_mixer_zo</v>
       </c>
       <c r="C64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" t="s">
         <v>338</v>
       </c>
-      <c r="D64" t="s">
+      <c r="G64" t="str">
+        <f t="shared" si="1"/>
+        <v>static mixer</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G64" t="str">
-        <f t="shared" si="1"/>
-        <v>static mixer</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A65" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="0"/>
         <v>storage_tank_zo</v>
       </c>
       <c r="C65" t="s">
+        <v>340</v>
+      </c>
+      <c r="D65" t="s">
+        <v>228</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="1"/>
+        <v>storage tank</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="D65" t="s">
-        <v>229</v>
-      </c>
-      <c r="G65" t="str">
-        <f t="shared" si="1"/>
-        <v>storage tank</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A66" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" ref="B66:B77" si="6">CONCATENATE(A66,"_zo")</f>
         <v>surface_discharge_zo</v>
       </c>
       <c r="C66" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" t="s">
         <v>343</v>
-      </c>
-      <c r="D66" t="s">
-        <v>344</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" ref="G66:G77" si="7">CONCATENATE(C66," ",D66)</f>
         <v>surface discharge</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="6"/>
         <v>sw_onshore_intake_zo</v>
       </c>
       <c r="C67" t="s">
+        <v>345</v>
+      </c>
+      <c r="D67" t="s">
         <v>346</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>347</v>
-      </c>
-      <c r="E67" t="s">
-        <v>348</v>
       </c>
       <c r="G67" t="str">
         <f>CONCATENATE(C67," ",D67," ",E67)</f>
         <v>sw onshore intake</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" si="6"/>
         <v>tramp_oil_tank_zo</v>
       </c>
       <c r="C68" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" t="s">
         <v>350</v>
       </c>
-      <c r="D68" t="s">
-        <v>351</v>
-      </c>
       <c r="E68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" ref="G68:G69" si="8">CONCATENATE(C68," ",D68," ",E68)</f>
         <v>tramp oil tank</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="6"/>
         <v>tri_media_filtration_zo</v>
       </c>
       <c r="C69" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="8"/>
         <v>tri media filtration</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="6"/>
         <v>ultra_filtration_zo</v>
       </c>
       <c r="C70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D70" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="7"/>
         <v>ultra filtration</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="6"/>
         <v>uv_aop_zo</v>
       </c>
       <c r="C71" t="s">
+        <v>356</v>
+      </c>
+      <c r="D71" t="s">
         <v>357</v>
-      </c>
-      <c r="D71" t="s">
-        <v>358</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="7"/>
         <v>uv aop</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="6"/>
         <v>uv_zo</v>
       </c>
       <c r="C72" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">uv </v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="6"/>
         <v>vfa_recovery_zo</v>
       </c>
       <c r="C73" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="7"/>
         <v>vfa recovery</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="6"/>
         <v>waiv_zo</v>
       </c>
       <c r="C74" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">waiv </v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="6"/>
         <v>walnut_shell_filter_zo</v>
       </c>
       <c r="C75" t="s">
+        <v>362</v>
+      </c>
+      <c r="D75" t="s">
         <v>363</v>
       </c>
-      <c r="D75" t="s">
-        <v>364</v>
-      </c>
       <c r="E75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" ref="G75:G76" si="9">CONCATENATE(C75," ",D75," ",E75)</f>
         <v>walnut shell filter</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="6"/>
         <v>water_pumping_station_zo</v>
       </c>
       <c r="C76" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D76" t="s">
+        <v>365</v>
+      </c>
+      <c r="E76" t="s">
         <v>366</v>
-      </c>
-      <c r="E76" t="s">
-        <v>367</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="9"/>
         <v>water pumping station</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="6"/>
         <v>well_field_zo</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="7"/>
@@ -6640,649 +6568,649 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:C80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="37.19921875" customWidth="1"/>
+    <col min="2" max="2" width="37.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C5" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.45">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.45">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.45">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.45">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.45">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.45">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.45">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.45">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.45">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.45">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.45">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.45">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.45">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.45">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.45">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.45">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>103</v>
       </c>
       <c r="C38" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>455</v>
+      </c>
+      <c r="C39" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>456</v>
-      </c>
-      <c r="C39" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.45">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.45">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.45">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.45">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.45">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>118</v>
       </c>
       <c r="C45" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.45">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.45">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.45">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.45">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>128</v>
       </c>
       <c r="C49" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C50" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>134</v>
-      </c>
-      <c r="C52" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>370</v>
-      </c>
-      <c r="C54" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.45">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C57" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" t="s">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>158</v>
-      </c>
-      <c r="C62" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>161</v>
-      </c>
-      <c r="C63" t="s">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>163</v>
-      </c>
-      <c r="C64" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>165</v>
-      </c>
-      <c r="C65" t="s">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>166</v>
+      </c>
+      <c r="C66" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>456</v>
+      </c>
+      <c r="C68" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>167</v>
-      </c>
-      <c r="C66" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B67" t="s">
-        <v>169</v>
-      </c>
-      <c r="C67" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B68" t="s">
-        <v>457</v>
-      </c>
-      <c r="C68" t="s">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>182</v>
+      </c>
+      <c r="C74" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>188</v>
+      </c>
+      <c r="C76" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B69" t="s">
-        <v>172</v>
-      </c>
-      <c r="C69" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B70" t="s">
-        <v>175</v>
-      </c>
-      <c r="C70" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B71" t="s">
-        <v>177</v>
-      </c>
-      <c r="C71" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B72" t="s">
-        <v>179</v>
-      </c>
-      <c r="C72" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B73" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C74" t="s">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>190</v>
+      </c>
+      <c r="C77" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C78" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B75" t="s">
-        <v>186</v>
-      </c>
-      <c r="C75" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B76" t="s">
-        <v>189</v>
-      </c>
-      <c r="C76" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B77" t="s">
-        <v>191</v>
-      </c>
-      <c r="C77" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B78" t="s">
-        <v>193</v>
-      </c>
-      <c r="C78" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
         <v>439</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B80" t="s">
-        <v>197</v>
-      </c>
-      <c r="C80" t="s">
-        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -7292,4 +7220,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
+++ b/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C43B9EE-BEE0-BB49-8E61-51C4620CFE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C1B3F5-E496-E348-B5C9-5A5374BB4600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10580" yWindow="2740" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$92</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="515">
   <si>
     <t>Name</t>
   </si>
@@ -1565,6 +1565,18 @@
   </si>
   <si>
     <t>cost_electrocoagulation</t>
+  </si>
+  <si>
+    <t>crystallizer_zo</t>
+  </si>
+  <si>
+    <t>CrystallizerZO</t>
+  </si>
+  <si>
+    <t>cost_crystallizer</t>
+  </si>
+  <si>
+    <t>crystallizer</t>
   </si>
 </sst>
 </file>
@@ -1938,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -2011,11 +2023,11 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I2" t="str">
-        <f t="shared" ref="I2:I38" si="1">IF(E2="SIDO","single-input, double-output",IF(E2="SISO","single-input, single-output",IF(E2="PT","pass-through",IF(E2="DISO","double-input, single-output",IF(E2="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <f t="shared" ref="I2:I39" si="1">IF(E2="SIDO","single-input, double-output",IF(E2="SISO","single-input, single-output",IF(E2="PT","pass-through",IF(E2="DISO","double-input, single-output",IF(E2="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
         <v>single-input, double-output</v>
       </c>
       <c r="J2" t="str">
-        <f t="shared" ref="J2:J38" si="2">IF(E2="SIDO","sido_methods",IF(E2="SISO","siso_methods",IF(E2="PT","pt_methods",IF(E2="DISO","diso_methods",IF(E2="SIDO reactive","sidor_methods","")))))</f>
+        <f t="shared" ref="J2:J39" si="2">IF(E2="SIDO","sido_methods",IF(E2="SISO","siso_methods",IF(E2="PT","pt_methods",IF(E2="DISO","diso_methods",IF(E2="SIDO reactive","sidor_methods","")))))</f>
         <v>sido_methods</v>
       </c>
     </row>
@@ -2883,254 +2895,254 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>514</v>
+      </c>
+      <c r="B28" t="s">
+        <v>511</v>
+      </c>
+      <c r="C28" t="s">
+        <v>512</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" t="s">
+        <v>513</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" ref="I28" si="3">IF(E28="SIDO","single-input, double-output",IF(E28="SISO","single-input, single-output",IF(E28="PT","pass-through",IF(E28="DISO","double-input, single-output",IF(E28="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" ref="J28" si="4">IF(E28="SIDO","sido_methods",IF(E28="SISO","siso_methods",IF(E28="PT","pt_methods",IF(E28="DISO","diso_methods",IF(E28="SIDO reactive","sidor_methods","")))))</f>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>67</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>390</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>26</v>
       </c>
-      <c r="F28" t="b">
+      <c r="F29" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G29" t="s">
         <v>12</v>
       </c>
-      <c r="H28" t="str">
-        <f>IF(D28="basic","cost_power_law_flow")</f>
+      <c r="H29" t="str">
+        <f>IF(D29="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
-      <c r="I28" t="str">
+      <c r="I29" t="str">
         <f t="shared" si="1"/>
         <v>single-input, single-output</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J29" t="str">
         <f t="shared" si="2"/>
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>69</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>379</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>30</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>27</v>
       </c>
-      <c r="F29" t="b">
+      <c r="F30" t="b">
         <v>1</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" t="s">
         <v>21</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H30" t="s">
         <v>70</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I30" t="str">
         <f t="shared" si="1"/>
         <v>pass-through</v>
       </c>
-      <c r="J29" t="str">
+      <c r="J30" t="str">
         <f t="shared" si="2"/>
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>71</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>391</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>10</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F30" t="b">
+      <c r="F31" t="b">
         <v>1</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G31" t="s">
         <v>12</v>
       </c>
-      <c r="H30" t="str">
-        <f>IF(D30="basic","cost_power_law_flow")</f>
+      <c r="H31" t="str">
+        <f>IF(D31="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
-      <c r="I30" t="str">
+      <c r="I31" t="str">
         <f t="shared" si="1"/>
         <v>single-input, double-output</v>
       </c>
-      <c r="J30" t="str">
+      <c r="J31" t="str">
         <f t="shared" si="2"/>
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>380</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>57</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>18</v>
       </c>
-      <c r="F31" t="b">
+      <c r="F32" t="b">
         <v>1</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G32" t="s">
         <v>12</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H32" t="s">
         <v>75</v>
       </c>
-      <c r="I31" t="str">
+      <c r="I32" t="str">
         <f t="shared" si="1"/>
         <v>reactive single-inlet, double-outlet</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J32" t="str">
         <f t="shared" si="2"/>
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>76</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>77</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>429</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>10</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F32" t="b">
+      <c r="F33" t="b">
         <v>1</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G33" t="s">
         <v>12</v>
       </c>
-      <c r="H32" t="str">
-        <f>IF(D32="basic","cost_power_law_flow")</f>
+      <c r="H33" t="str">
+        <f>IF(D33="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
-      <c r="I32" t="str">
+      <c r="I33" t="str">
         <f t="shared" si="1"/>
         <v>single-input, double-output</v>
       </c>
-      <c r="J32" t="str">
+      <c r="J33" t="str">
         <f t="shared" si="2"/>
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>78</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>79</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>394</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>30</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>18</v>
       </c>
-      <c r="F33" t="b">
+      <c r="F34" t="b">
         <v>0</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>31</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H34" t="s">
         <v>80</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I34" t="str">
         <f t="shared" si="1"/>
         <v>reactive single-inlet, double-outlet</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J34" t="str">
         <f t="shared" si="2"/>
         <v>sidor_methods</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>507</v>
-      </c>
-      <c r="B34" t="s">
-        <v>508</v>
-      </c>
-      <c r="C34" t="s">
-        <v>509</v>
-      </c>
-      <c r="D34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" t="s">
-        <v>510</v>
-      </c>
-      <c r="I34" t="str">
-        <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J34" t="str">
-        <f t="shared" si="2"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="C35" t="s">
-        <v>381</v>
+        <v>509</v>
       </c>
       <c r="D35" t="s">
         <v>30</v>
@@ -3145,7 +3157,7 @@
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>65</v>
+        <v>510</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="1"/>
@@ -3158,54 +3170,53 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" t="str">
-        <f>IF(D36="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -3213,33 +3224,34 @@
       <c r="G37" t="s">
         <v>12</v>
       </c>
-      <c r="H37" t="s">
-        <v>87</v>
+      <c r="H37" t="str">
+        <f>IF(D37="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -3247,163 +3259,163 @@
       <c r="G38" t="s">
         <v>12</v>
       </c>
-      <c r="H38" t="str">
-        <f>IF(D38="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H38" t="s">
+        <v>87</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="F39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H39" t="b">
+        <v>12</v>
+      </c>
+      <c r="H39" t="str">
         <f>IF(D39="basic","cost_power_law_flow")</f>
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
-        <v>93</v>
-      </c>
-      <c r="J39" t="s">
-        <v>93</v>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="1"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="2"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>437</v>
+        <v>393</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40" t="s">
-        <v>96</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" ref="I40:I45" si="3">IF(E40="SIDO","single-input, double-output",IF(E40="SISO","single-input, single-output",IF(E40="PT","pass-through",IF(E40="DISO","double-input, single-output",IF(E40="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J40" t="str">
-        <f t="shared" ref="J40:J45" si="4">IF(E40="SIDO","sido_methods",IF(E40="SISO","siso_methods",IF(E40="PT","pt_methods",IF(E40="DISO","diso_methods",IF(E40="SIDO reactive","sidor_methods","")))))</f>
-        <v>sido_methods</v>
+        <v>58</v>
+      </c>
+      <c r="H40" t="b">
+        <f>IF(D40="basic","cost_power_law_flow")</f>
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="D41" t="s">
         <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="3"/>
-        <v>single-input, single-output</v>
+        <f t="shared" ref="I41:I46" si="5">IF(E41="SIDO","single-input, double-output",IF(E41="SISO","single-input, single-output",IF(E41="PT","pass-through",IF(E41="DISO","double-input, single-output",IF(E41="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <v>single-input, double-output</v>
       </c>
       <c r="J41" t="str">
-        <f t="shared" si="4"/>
-        <v>siso_methods</v>
+        <f t="shared" ref="J41:J46" si="6">IF(E41="SIDO","sido_methods",IF(E41="SISO","siso_methods",IF(E41="PT","pt_methods",IF(E41="DISO","diso_methods",IF(E41="SIDO reactive","sidor_methods","")))))</f>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D42" t="s">
         <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H42" t="s">
-        <v>506</v>
+        <v>99</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="3"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>single-input, single-output</v>
       </c>
       <c r="J42" t="str">
-        <f t="shared" si="4"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="D43" t="s">
         <v>30</v>
@@ -3412,69 +3424,69 @@
         <v>11</v>
       </c>
       <c r="F43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="H43" t="s">
+        <v>506</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>474</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>473</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" t="s">
-        <v>476</v>
+        <v>21</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="3"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J44" t="str">
-        <f t="shared" si="4"/>
-        <v>sidor_methods</v>
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B45" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="C45" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>18</v>
@@ -3483,64 +3495,63 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>sidor_methods</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>477</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>455</v>
       </c>
       <c r="C46" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" t="str">
-        <f>IF(D46="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>478</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" ref="I46:I91" si="5">IF(E46="SIDO","single-input, double-output",IF(E46="SISO","single-input, single-output",IF(E46="PT","pass-through",IF(E46="DISO","double-input, single-output",IF(E46="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
-        <v>pass-through</v>
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J46" t="str">
-        <f t="shared" ref="J46:J91" si="6">IF(E46="SIDO","sido_methods",IF(E46="SISO","siso_methods",IF(E46="PT","pt_methods",IF(E46="DISO","diso_methods",IF(E46="SIDO reactive","sidor_methods","")))))</f>
-        <v>pt_methods</v>
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -3559,57 +3570,58 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="I47:I92" si="7">IF(E47="SIDO","single-input, double-output",IF(E47="SISO","single-input, single-output",IF(E47="PT","pass-through",IF(E47="DISO","double-input, single-output",IF(E47="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
         <v>pass-through</v>
       </c>
       <c r="J47" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J47:J92" si="8">IF(E47="SIDO","sido_methods",IF(E47="SISO","siso_methods",IF(E47="PT","pt_methods",IF(E47="DISO","diso_methods",IF(E47="SIDO reactive","sidor_methods","")))))</f>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" t="s">
-        <v>110</v>
+        <v>12</v>
+      </c>
+      <c r="H48" t="str">
+        <f>IF(D48="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J48" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D49" t="s">
         <v>30</v>
@@ -3618,72 +3630,72 @@
         <v>11</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H49" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J49" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J50" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -3692,26 +3704,26 @@
         <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J51" t="str">
-        <f t="shared" si="6"/>
-        <v>sidor_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>479</v>
+        <v>117</v>
       </c>
       <c r="B52" t="s">
-        <v>480</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>481</v>
+        <v>399</v>
       </c>
       <c r="D52" t="s">
         <v>30</v>
@@ -3726,32 +3738,32 @@
         <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>482</v>
+        <v>119</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sidor_methods</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>480</v>
       </c>
       <c r="C53" t="s">
-        <v>400</v>
+        <v>481</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -3759,28 +3771,27 @@
       <c r="G53" t="s">
         <v>12</v>
       </c>
-      <c r="H53" t="str">
-        <f>IF(D53="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H53" t="s">
+        <v>482</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -3799,26 +3810,26 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>483</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>484</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>485</v>
+        <v>401</v>
       </c>
       <c r="D55" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>11</v>
@@ -3829,61 +3840,62 @@
       <c r="G55" t="s">
         <v>12</v>
       </c>
-      <c r="H55" t="s">
-        <v>486</v>
+      <c r="H55" t="str">
+        <f>IF(D55="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>484</v>
       </c>
       <c r="C56" t="s">
-        <v>385</v>
+        <v>485</v>
       </c>
       <c r="D56" t="s">
         <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>126</v>
+        <v>486</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="6"/>
-        <v>sidor_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>487</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>488</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>489</v>
+        <v>385</v>
       </c>
       <c r="D57" t="s">
         <v>30</v>
@@ -3892,38 +3904,38 @@
         <v>18</v>
       </c>
       <c r="F57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>490</v>
+        <v>126</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sidor_methods</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>488</v>
       </c>
       <c r="C58" t="s">
-        <v>402</v>
+        <v>489</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E58" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -3931,62 +3943,62 @@
       <c r="G58" t="s">
         <v>12</v>
       </c>
-      <c r="H58" t="str">
-        <f>IF(D58="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H58" t="s">
+        <v>490</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J58" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C59" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" t="s">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="H59" t="str">
+        <f>IF(D59="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J59" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -3998,70 +4010,70 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
-      </c>
-      <c r="H60" t="str">
-        <f>IF(D60="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>21</v>
+      </c>
+      <c r="H60" t="s">
+        <v>65</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D61" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" t="s">
-        <v>136</v>
+        <v>12</v>
+      </c>
+      <c r="H61" t="str">
+        <f>IF(D61="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J61" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="D62" t="s">
         <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -4070,26 +4082,26 @@
         <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, single-output</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J62" t="str">
-        <f t="shared" si="6"/>
-        <v>siso_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>369</v>
       </c>
       <c r="C63" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D63" t="s">
         <v>30</v>
@@ -4104,204 +4116,203 @@
         <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, single-output</v>
       </c>
       <c r="J63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>siso_methods</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>491</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>492</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
-        <v>493</v>
+        <v>424</v>
       </c>
       <c r="D64" t="s">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>494</v>
+        <v>141</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <f t="shared" si="7"/>
+        <v>single-input, single-output</v>
       </c>
       <c r="J64" t="str">
-        <f t="shared" si="6"/>
-        <v>sidor_methods</v>
+        <f t="shared" si="8"/>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>492</v>
       </c>
       <c r="C65" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="D65" t="s">
         <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>144</v>
+        <v>494</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J65" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" t="str">
-        <f>IF(D66="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
+        <v>144</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J66" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>31</v>
-      </c>
-      <c r="H67" t="s">
-        <v>149</v>
+        <v>12</v>
+      </c>
+      <c r="H67" t="str">
+        <f>IF(D67="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D68" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>12</v>
-      </c>
-      <c r="H68" t="str">
-        <f>IF(D68="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>149</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D69" t="s">
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -4314,26 +4325,26 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
@@ -4344,30 +4355,31 @@
       <c r="G70" t="s">
         <v>12</v>
       </c>
-      <c r="H70" t="s">
-        <v>65</v>
+      <c r="H70" t="str">
+        <f>IF(D70="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J70" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C71" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
@@ -4379,29 +4391,29 @@
         <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J71" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
@@ -4412,28 +4424,27 @@
       <c r="G72" t="s">
         <v>12</v>
       </c>
-      <c r="H72" t="str">
-        <f>IF(D72="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H72" t="s">
+        <v>158</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
@@ -4452,29 +4463,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="D74" t="s">
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -4487,23 +4498,23 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J74" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
@@ -4522,26 +4533,26 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -4552,30 +4563,31 @@
       <c r="G76" t="s">
         <v>12</v>
       </c>
-      <c r="H76" t="s">
-        <v>169</v>
+      <c r="H76" t="str">
+        <f>IF(D76="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J76" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>495</v>
+        <v>167</v>
       </c>
       <c r="B77" t="s">
-        <v>496</v>
+        <v>168</v>
       </c>
       <c r="C77" t="s">
-        <v>497</v>
+        <v>430</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -4587,32 +4599,32 @@
         <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>498</v>
+        <v>169</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B78" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C78" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -4621,97 +4633,97 @@
         <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J78" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B79" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="C79" t="s">
-        <v>452</v>
+        <v>501</v>
       </c>
       <c r="D79" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H79" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J79" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>456</v>
       </c>
       <c r="C80" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D80" t="s">
         <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H80" t="s">
-        <v>172</v>
+        <v>504</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J80" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -4722,28 +4734,27 @@
       <c r="G81" t="s">
         <v>21</v>
       </c>
-      <c r="H81" t="str">
-        <f>IF(D81="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H81" t="s">
+        <v>172</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J81" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C82" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
@@ -4755,36 +4766,36 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H82" t="str">
         <f>IF(D82="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
       <c r="J82" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C83" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D83" t="s">
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -4797,23 +4808,23 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
       </c>
       <c r="J83" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
@@ -4832,29 +4843,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -4862,27 +4873,28 @@
       <c r="G85" t="s">
         <v>12</v>
       </c>
-      <c r="H85" t="s">
-        <v>183</v>
+      <c r="H85" t="str">
+        <f>IF(D85="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, single-output</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J85" t="str">
-        <f t="shared" si="6"/>
-        <v>siso_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C86" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D86" t="s">
         <v>30</v>
@@ -4897,32 +4909,32 @@
         <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, single-output</v>
       </c>
       <c r="J86" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>siso_methods</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -4931,29 +4943,29 @@
         <v>12</v>
       </c>
       <c r="H87" t="s">
-        <v>460</v>
+        <v>186</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="5"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="7"/>
+        <v>single-input, single-output</v>
       </c>
       <c r="J87" t="str">
-        <f t="shared" si="6"/>
-        <v>sido_methods</v>
+        <f t="shared" si="8"/>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -4964,28 +4976,27 @@
       <c r="G88" t="s">
         <v>12</v>
       </c>
-      <c r="H88" t="str">
-        <f>IF(D88="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H88" t="s">
+        <v>460</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J88" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
@@ -5004,57 +5015,58 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J89" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>31</v>
-      </c>
-      <c r="H90" t="s">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="H90" t="str">
+        <f>IF(D90="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="5"/>
-        <v>pass-through</v>
+        <f t="shared" si="7"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J90" t="str">
-        <f t="shared" si="6"/>
-        <v>pt_methods</v>
+        <f t="shared" si="8"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B91" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D91" t="s">
         <v>30</v>
@@ -5063,26 +5075,60 @@
         <v>27</v>
       </c>
       <c r="F91" t="b">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>31</v>
+      </c>
+      <c r="H91" t="s">
+        <v>65</v>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="7"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J91" t="str">
+        <f t="shared" si="8"/>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>195</v>
+      </c>
+      <c r="B92" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" t="s">
+        <v>439</v>
+      </c>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" t="b">
         <v>1</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G92" t="s">
         <v>21</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H92" t="s">
         <v>197</v>
       </c>
-      <c r="I91" t="str">
-        <f t="shared" si="5"/>
+      <c r="I92" t="str">
+        <f t="shared" si="7"/>
         <v>pass-through</v>
       </c>
-      <c r="J91" t="str">
-        <f t="shared" si="6"/>
+      <c r="J92" t="str">
+        <f t="shared" si="8"/>
         <v>pt_methods</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J91">
-    <sortCondition ref="B2:B91"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J92">
+    <sortCondition ref="B2:B92"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
+++ b/docs/technical_reference/unit_models/zero_order_unit_models/WT3_unit_classification_for_doc.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C1B3F5-E496-E348-B5C9-5A5374BB4600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F101314-FCC5-314E-ADA5-DE8EBF68B42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10580" yWindow="2740" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="511">
   <si>
     <t>Name</t>
   </si>
@@ -73,9 +73,6 @@
     <t>constant_intensity</t>
   </si>
   <si>
-    <t>air flotation</t>
-  </si>
-  <si>
     <t>air_flotation_zo</t>
   </si>
   <si>
@@ -421,6 +418,9 @@
     <t>microfiltration_zo</t>
   </si>
   <si>
+    <t>microscreen filtration</t>
+  </si>
+  <si>
     <t>microscreen_filtration_zo</t>
   </si>
   <si>
@@ -1565,18 +1565,6 @@
   </si>
   <si>
     <t>cost_electrocoagulation</t>
-  </si>
-  <si>
-    <t>crystallizer_zo</t>
-  </si>
-  <si>
-    <t>CrystallizerZO</t>
-  </si>
-  <si>
-    <t>cost_crystallizer</t>
-  </si>
-  <si>
-    <t>crystallizer</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -2019,27 +2007,27 @@
         <v>12</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H11" si="0">IF(D2="basic","cost_power_law_flow")</f>
+        <f t="shared" ref="H2:H10" si="0">IF(D2="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
       <c r="I2" t="str">
-        <f t="shared" ref="I2:I39" si="1">IF(E2="SIDO","single-input, double-output",IF(E2="SISO","single-input, single-output",IF(E2="PT","pass-through",IF(E2="DISO","double-input, single-output",IF(E2="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <f t="shared" ref="I2:I37" si="1">IF(E2="SIDO","single-input, double-output",IF(E2="SISO","single-input, single-output",IF(E2="PT","pass-through",IF(E2="DISO","double-input, single-output",IF(E2="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
         <v>single-input, double-output</v>
       </c>
       <c r="J2" t="str">
-        <f t="shared" ref="J2:J39" si="2">IF(E2="SIDO","sido_methods",IF(E2="SISO","siso_methods",IF(E2="PT","pt_methods",IF(E2="DISO","diso_methods",IF(E2="SIDO reactive","sidor_methods","")))))</f>
+        <f t="shared" ref="J2:J37" si="2">IF(E2="SIDO","sido_methods",IF(E2="SISO","siso_methods",IF(E2="PT","pt_methods",IF(E2="DISO","diso_methods",IF(E2="SIDO reactive","sidor_methods","")))))</f>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>505</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2054,7 +2042,7 @@
         <v>12</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D3="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
       <c r="I3" t="str">
@@ -2068,19 +2056,19 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>463</v>
       </c>
       <c r="C4" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -2088,43 +2076,42 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="str">
-        <f>IF(D4="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H4" t="s">
+        <v>64</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>463</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>457</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="1"/>
@@ -2137,28 +2124,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>464</v>
       </c>
       <c r="B6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>445</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
       <c r="H6" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="1"/>
@@ -2171,47 +2158,48 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>454</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>446</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>465</v>
+        <v>20</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="1"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="2"/>
-        <v>sidor_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -2223,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
@@ -2240,19 +2228,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -2266,22 +2254,22 @@
       </c>
       <c r="I9" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>371</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>370</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -2301,163 +2289,163 @@
       </c>
       <c r="I10" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, single-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="2"/>
-        <v>siso_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="0"/>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(D12="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" t="str">
-        <f>IF(D13="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" t="s">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="H14" t="str">
+        <f>IF(D14="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="1"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="2"/>
-        <v>sidor_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>466</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>467</v>
       </c>
       <c r="C15" t="s">
-        <v>388</v>
+        <v>468</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -2468,9 +2456,8 @@
       <c r="G15" t="s">
         <v>12</v>
       </c>
-      <c r="H15" t="str">
-        <f>IF(D15="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H15" t="s">
+        <v>469</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="1"/>
@@ -2483,87 +2470,87 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>466</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>467</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>30</v>
       </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>12</v>
-      </c>
       <c r="H16" t="s">
-        <v>469</v>
+        <v>41</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>387</v>
+        <v>432</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -2571,27 +2558,28 @@
       <c r="G18" t="s">
         <v>12</v>
       </c>
-      <c r="H18" t="s">
-        <v>45</v>
+      <c r="H18" t="str">
+        <f>IF(D18="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, single-output</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="2"/>
-        <v>siso_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>470</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>471</v>
       </c>
       <c r="C19" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -2605,9 +2593,8 @@
       <c r="G19" t="s">
         <v>12</v>
       </c>
-      <c r="H19" t="str">
-        <f>IF(D19="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H19" t="s">
+        <v>64</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="1"/>
@@ -2620,19 +2607,19 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>470</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>471</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -2640,43 +2627,43 @@
       <c r="G20" t="s">
         <v>12</v>
       </c>
-      <c r="H20" t="s">
-        <v>65</v>
+      <c r="H20" t="str">
+        <f>IF(D20="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" t="str">
-        <f>IF(D21="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" si="1"/>
@@ -2689,121 +2676,122 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>458</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="H23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="1"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="2"/>
-        <v>sidor_methods</v>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" t="s">
-        <v>459</v>
+        <v>12</v>
+      </c>
+      <c r="H24" t="str">
+        <f>IF(D24="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, single-output</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="2"/>
-        <v>siso_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -2817,28 +2805,28 @@
       </c>
       <c r="I25" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -2846,34 +2834,33 @@
       <c r="G26" t="s">
         <v>12</v>
       </c>
-      <c r="H26" t="str">
-        <f>IF(D26="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H26" t="s">
+        <v>64</v>
       </c>
       <c r="I26" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J26" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -2881,67 +2868,68 @@
       <c r="G27" t="s">
         <v>12</v>
       </c>
-      <c r="H27" t="s">
-        <v>65</v>
+      <c r="H27" t="str">
+        <f>IF(D27="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I27" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>single-input, single-output</v>
       </c>
       <c r="J27" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>514</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>511</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>512</v>
+        <v>379</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>513</v>
+        <v>69</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" ref="I28" si="3">IF(E28="SIDO","single-input, double-output",IF(E28="SISO","single-input, single-output",IF(E28="PT","pass-through",IF(E28="DISO","double-input, single-output",IF(E28="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
-        <v>single-input, double-output</v>
+        <f t="shared" si="1"/>
+        <v>pass-through</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" ref="J28" si="4">IF(E28="SIDO","sido_methods",IF(E28="SISO","siso_methods",IF(E28="PT","pt_methods",IF(E28="DISO","diso_methods",IF(E28="SIDO reactive","sidor_methods","")))))</f>
-        <v>sido_methods</v>
+        <f t="shared" si="2"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -2955,56 +2943,56 @@
       </c>
       <c r="I29" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, single-output</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J29" t="str">
         <f t="shared" si="2"/>
-        <v>siso_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I30" t="str">
         <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <v>reactive single-inlet, double-outlet</v>
       </c>
       <c r="J30" t="str">
         <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <v>sidor_methods</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -3033,28 +3021,28 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I32" t="str">
         <f t="shared" si="1"/>
@@ -3067,29 +3055,28 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>507</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>508</v>
       </c>
       <c r="C33" t="s">
-        <v>429</v>
+        <v>509</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" t="str">
-        <f>IF(D33="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H33" t="s">
+        <v>510</v>
       </c>
       <c r="I33" t="str">
         <f t="shared" si="1"/>
@@ -3102,96 +3089,97 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="1"/>
-        <v>reactive single-inlet, double-outlet</v>
+        <v>single-input, double-output</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="2"/>
-        <v>sidor_methods</v>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>507</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>509</v>
+        <v>395</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" t="s">
-        <v>510</v>
+        <v>12</v>
+      </c>
+      <c r="H35" t="str">
+        <f>IF(D35="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
+        <v>pass-through</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="D36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="1"/>
@@ -3204,19 +3192,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -3239,118 +3227,117 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" t="str">
-        <f t="shared" si="1"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J38" t="str">
-        <f t="shared" si="2"/>
-        <v>sido_methods</v>
+        <v>57</v>
+      </c>
+      <c r="H38" t="b">
+        <f>IF(D38="basic","cost_power_law_flow")</f>
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>92</v>
+      </c>
+      <c r="J38" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>437</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" t="str">
-        <f>IF(D39="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H39" t="s">
+        <v>95</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="1"/>
-        <v>pass-through</v>
+        <f t="shared" ref="I39:I44" si="3">IF(E39="SIDO","single-input, double-output",IF(E39="SISO","single-input, single-output",IF(E39="PT","pass-through",IF(E39="DISO","double-input, single-output",IF(E39="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <v>single-input, double-output</v>
       </c>
       <c r="J39" t="str">
-        <f t="shared" si="2"/>
-        <v>pt_methods</v>
+        <f t="shared" ref="J39:J44" si="4">IF(E39="SIDO","sido_methods",IF(E39="SISO","siso_methods",IF(E39="PT","pt_methods",IF(E39="DISO","diso_methods",IF(E39="SIDO reactive","sidor_methods","")))))</f>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
-      </c>
-      <c r="H40" t="b">
-        <f>IF(D40="basic","cost_power_law_flow")</f>
-        <v>0</v>
-      </c>
-      <c r="I40" t="s">
-        <v>93</v>
-      </c>
-      <c r="J40" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="H40" t="s">
+        <v>98</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="3"/>
+        <v>single-input, single-output</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
@@ -3359,960 +3346,962 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>96</v>
+        <v>506</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" ref="I41:I46" si="5">IF(E41="SIDO","single-input, double-output",IF(E41="SISO","single-input, single-output",IF(E41="PT","pass-through",IF(E41="DISO","double-input, single-output",IF(E41="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <f t="shared" si="3"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J41" t="str">
-        <f t="shared" ref="J41:J46" si="6">IF(E41="SIDO","sido_methods",IF(E41="SISO","siso_methods",IF(E41="PT","pt_methods",IF(E41="DISO","diso_methods",IF(E41="SIDO reactive","sidor_methods","")))))</f>
+        <f t="shared" si="4"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="3"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>474</v>
+      </c>
+      <c r="B43" t="s">
+        <v>473</v>
+      </c>
+      <c r="C43" t="s">
+        <v>475</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
         <v>12</v>
       </c>
-      <c r="H42" t="s">
-        <v>99</v>
-      </c>
-      <c r="I42" t="str">
+      <c r="H43" t="s">
+        <v>476</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="3"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>477</v>
+      </c>
+      <c r="B44" t="s">
+        <v>455</v>
+      </c>
+      <c r="C44" t="s">
+        <v>451</v>
+      </c>
+      <c r="D44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>30</v>
+      </c>
+      <c r="H44" t="s">
+        <v>478</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="3"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" t="s">
+        <v>441</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" t="str">
+        <f>IF(D45="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" ref="I45:I91" si="5">IF(E45="SIDO","single-input, double-output",IF(E45="SISO","single-input, single-output",IF(E45="PT","pass-through",IF(E45="DISO","double-input, single-output",IF(E45="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
+        <v>pass-through</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" ref="J45:J91" si="6">IF(E45="SIDO","sido_methods",IF(E45="SISO","siso_methods",IF(E45="PT","pt_methods",IF(E45="DISO","diso_methods",IF(E45="SIDO reactive","sidor_methods","")))))</f>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>440</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" t="str">
+        <f>IF(D46="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" t="s">
+        <v>426</v>
+      </c>
+      <c r="D47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>396</v>
+      </c>
+      <c r="D48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" t="s">
+        <v>112</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" t="s">
+        <v>397</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" t="s">
+        <v>115</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" t="s">
+        <v>399</v>
+      </c>
+      <c r="D50" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" t="s">
+        <v>118</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>479</v>
+      </c>
+      <c r="B51" t="s">
+        <v>480</v>
+      </c>
+      <c r="C51" t="s">
+        <v>481</v>
+      </c>
+      <c r="D51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>482</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" t="s">
+        <v>400</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" t="str">
+        <f>IF(D52="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" t="s">
+        <v>401</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" t="str">
+        <f>IF(D53="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>483</v>
+      </c>
+      <c r="B54" t="s">
+        <v>484</v>
+      </c>
+      <c r="C54" t="s">
+        <v>485</v>
+      </c>
+      <c r="D54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" t="s">
+        <v>486</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" t="s">
+        <v>385</v>
+      </c>
+      <c r="D55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" t="s">
+        <v>125</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>487</v>
+      </c>
+      <c r="B56" t="s">
+        <v>488</v>
+      </c>
+      <c r="C56" t="s">
+        <v>489</v>
+      </c>
+      <c r="D56" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>490</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" t="s">
+        <v>402</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" t="str">
+        <f>IF(D57="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" t="s">
+        <v>403</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" t="str">
+        <f>IF(D58="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" t="s">
+        <v>423</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" t="s">
+        <v>64</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" t="s">
+        <v>404</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" t="str">
+        <f>IF(D60="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" t="s">
+        <v>405</v>
+      </c>
+      <c r="D61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>30</v>
+      </c>
+      <c r="H61" t="s">
+        <v>136</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" t="s">
+        <v>369</v>
+      </c>
+      <c r="C62" t="s">
+        <v>425</v>
+      </c>
+      <c r="D62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62" t="s">
+        <v>138</v>
+      </c>
+      <c r="I62" t="str">
         <f t="shared" si="5"/>
         <v>single-input, single-output</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J62" t="str">
         <f t="shared" si="6"/>
         <v>siso_methods</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" t="s">
-        <v>428</v>
-      </c>
-      <c r="D43" t="s">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" t="s">
+        <v>424</v>
+      </c>
+      <c r="D63" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
         <v>30</v>
       </c>
-      <c r="E43" t="s">
+      <c r="H63" t="s">
+        <v>141</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="5"/>
+        <v>single-input, single-output</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="6"/>
+        <v>siso_methods</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>491</v>
+      </c>
+      <c r="B64" t="s">
+        <v>492</v>
+      </c>
+      <c r="C64" t="s">
+        <v>493</v>
+      </c>
+      <c r="D64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" t="s">
+        <v>494</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="5"/>
+        <v>reactive single-inlet, double-outlet</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="6"/>
+        <v>sidor_methods</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" t="s">
+        <v>443</v>
+      </c>
+      <c r="D65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" t="s">
         <v>11</v>
       </c>
-      <c r="F43" t="b">
+      <c r="F65" t="b">
         <v>0</v>
       </c>
-      <c r="G43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" t="s">
-        <v>506</v>
-      </c>
-      <c r="I43" t="str">
+      <c r="G65" t="s">
+        <v>30</v>
+      </c>
+      <c r="H65" t="s">
+        <v>144</v>
+      </c>
+      <c r="I65" t="str">
         <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J65" t="str">
         <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" t="s">
-        <v>450</v>
-      </c>
-      <c r="D44" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" t="s">
+        <v>407</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" t="s">
         <v>11</v>
       </c>
-      <c r="F44" t="b">
+      <c r="F66" t="b">
         <v>1</v>
       </c>
-      <c r="G44" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="str">
+      <c r="G66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" t="str">
+        <f>IF(D66="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
+      </c>
+      <c r="I66" t="str">
         <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J66" t="str">
         <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>474</v>
-      </c>
-      <c r="B45" t="s">
-        <v>473</v>
-      </c>
-      <c r="C45" t="s">
-        <v>475</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" t="s">
-        <v>476</v>
-      </c>
-      <c r="I45" t="str">
-        <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J45" t="str">
-        <f t="shared" si="6"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>477</v>
-      </c>
-      <c r="B46" t="s">
-        <v>455</v>
-      </c>
-      <c r="C46" t="s">
-        <v>451</v>
-      </c>
-      <c r="D46" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46" t="s">
-        <v>478</v>
-      </c>
-      <c r="I46" t="str">
-        <f t="shared" si="5"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J46" t="str">
-        <f t="shared" si="6"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" t="s">
-        <v>441</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" t="str">
-        <f>IF(D47="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I47" t="str">
-        <f t="shared" ref="I47:I92" si="7">IF(E47="SIDO","single-input, double-output",IF(E47="SISO","single-input, single-output",IF(E47="PT","pass-through",IF(E47="DISO","double-input, single-output",IF(E47="SIDO reactive","reactive single-inlet, double-outlet","")))))</f>
-        <v>pass-through</v>
-      </c>
-      <c r="J47" t="str">
-        <f t="shared" ref="J47:J92" si="8">IF(E47="SIDO","sido_methods",IF(E47="SISO","siso_methods",IF(E47="PT","pt_methods",IF(E47="DISO","diso_methods",IF(E47="SIDO reactive","sidor_methods","")))))</f>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" t="s">
-        <v>107</v>
-      </c>
-      <c r="C48" t="s">
-        <v>440</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" t="str">
-        <f>IF(D48="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I48" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J48" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>108</v>
-      </c>
-      <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>426</v>
-      </c>
-      <c r="D49" t="s">
-        <v>30</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" t="s">
-        <v>110</v>
-      </c>
-      <c r="I49" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>396</v>
-      </c>
-      <c r="D50" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>31</v>
-      </c>
-      <c r="H50" t="s">
-        <v>113</v>
-      </c>
-      <c r="I50" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J50" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" t="s">
-        <v>397</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" t="s">
-        <v>116</v>
-      </c>
-      <c r="I51" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J51" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>117</v>
-      </c>
-      <c r="B52" t="s">
-        <v>118</v>
-      </c>
-      <c r="C52" t="s">
-        <v>399</v>
-      </c>
-      <c r="D52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" t="s">
-        <v>119</v>
-      </c>
-      <c r="I52" t="str">
-        <f t="shared" si="7"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J52" t="str">
-        <f t="shared" si="8"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>479</v>
-      </c>
-      <c r="B53" t="s">
-        <v>480</v>
-      </c>
-      <c r="C53" t="s">
-        <v>481</v>
-      </c>
-      <c r="D53" t="s">
-        <v>30</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>12</v>
-      </c>
-      <c r="H53" t="s">
-        <v>482</v>
-      </c>
-      <c r="I53" t="str">
-        <f t="shared" si="7"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J53" t="str">
-        <f t="shared" si="8"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>120</v>
-      </c>
-      <c r="B54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" t="s">
-        <v>400</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>12</v>
-      </c>
-      <c r="H54" t="str">
-        <f>IF(D54="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I54" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J54" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" t="s">
-        <v>401</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" t="str">
-        <f>IF(D55="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I55" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J55" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>483</v>
-      </c>
-      <c r="B56" t="s">
-        <v>484</v>
-      </c>
-      <c r="C56" t="s">
-        <v>485</v>
-      </c>
-      <c r="D56" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" t="s">
-        <v>486</v>
-      </c>
-      <c r="I56" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J56" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" t="s">
-        <v>385</v>
-      </c>
-      <c r="D57" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>31</v>
-      </c>
-      <c r="H57" t="s">
-        <v>126</v>
-      </c>
-      <c r="I57" t="str">
-        <f t="shared" si="7"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J57" t="str">
-        <f t="shared" si="8"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>487</v>
-      </c>
-      <c r="B58" t="s">
-        <v>488</v>
-      </c>
-      <c r="C58" t="s">
-        <v>489</v>
-      </c>
-      <c r="D58" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>12</v>
-      </c>
-      <c r="H58" t="s">
-        <v>490</v>
-      </c>
-      <c r="I58" t="str">
-        <f t="shared" si="7"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="8"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>127</v>
-      </c>
-      <c r="B59" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" t="s">
-        <v>402</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" t="str">
-        <f>IF(D59="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I59" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" t="s">
-        <v>423</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" t="s">
-        <v>65</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J60" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" t="s">
-        <v>404</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>12</v>
-      </c>
-      <c r="H61" t="str">
-        <f>IF(D61="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
-      </c>
-      <c r="I61" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J61" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" t="s">
-        <v>405</v>
-      </c>
-      <c r="D62" t="s">
-        <v>30</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>31</v>
-      </c>
-      <c r="H62" t="s">
-        <v>136</v>
-      </c>
-      <c r="I62" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>137</v>
-      </c>
-      <c r="B63" t="s">
-        <v>369</v>
-      </c>
-      <c r="C63" t="s">
-        <v>425</v>
-      </c>
-      <c r="D63" t="s">
-        <v>30</v>
-      </c>
-      <c r="E63" t="s">
-        <v>26</v>
-      </c>
-      <c r="F63" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
-        <v>31</v>
-      </c>
-      <c r="H63" t="s">
-        <v>138</v>
-      </c>
-      <c r="I63" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, single-output</v>
-      </c>
-      <c r="J63" t="str">
-        <f t="shared" si="8"/>
-        <v>siso_methods</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>139</v>
-      </c>
-      <c r="B64" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" t="s">
-        <v>424</v>
-      </c>
-      <c r="D64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" t="s">
-        <v>26</v>
-      </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" t="s">
-        <v>31</v>
-      </c>
-      <c r="H64" t="s">
-        <v>141</v>
-      </c>
-      <c r="I64" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, single-output</v>
-      </c>
-      <c r="J64" t="str">
-        <f t="shared" si="8"/>
-        <v>siso_methods</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>491</v>
-      </c>
-      <c r="B65" t="s">
-        <v>492</v>
-      </c>
-      <c r="C65" t="s">
-        <v>493</v>
-      </c>
-      <c r="D65" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>12</v>
-      </c>
-      <c r="H65" t="s">
-        <v>494</v>
-      </c>
-      <c r="I65" t="str">
-        <f t="shared" si="7"/>
-        <v>reactive single-inlet, double-outlet</v>
-      </c>
-      <c r="J65" t="str">
-        <f t="shared" si="8"/>
-        <v>sidor_methods</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
-      </c>
-      <c r="C66" t="s">
-        <v>443</v>
-      </c>
-      <c r="D66" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>31</v>
-      </c>
-      <c r="H66" t="s">
-        <v>144</v>
-      </c>
-      <c r="I66" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
-      </c>
-      <c r="J66" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
-      </c>
-    </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
-      </c>
-      <c r="H67" t="str">
-        <f>IF(D67="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H67" t="s">
+        <v>149</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C68" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
-      </c>
-      <c r="H68" t="s">
-        <v>149</v>
+        <v>12</v>
+      </c>
+      <c r="H68" t="str">
+        <f>IF(D68="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D69" t="s">
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -4325,26 +4314,26 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
@@ -4355,31 +4344,30 @@
       <c r="G70" t="s">
         <v>12</v>
       </c>
-      <c r="H70" t="str">
-        <f>IF(D70="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H70" t="s">
+        <v>64</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J70" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
@@ -4391,29 +4379,29 @@
         <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J71" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D72" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
@@ -4424,27 +4412,28 @@
       <c r="G72" t="s">
         <v>12</v>
       </c>
-      <c r="H72" t="s">
-        <v>158</v>
+      <c r="H72" t="str">
+        <f>IF(D72="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
@@ -4463,29 +4452,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="D74" t="s">
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -4498,29 +4487,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
       </c>
       <c r="J74" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -4533,29 +4522,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -4563,34 +4552,33 @@
       <c r="G76" t="s">
         <v>12</v>
       </c>
-      <c r="H76" t="str">
-        <f>IF(D76="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H76" t="s">
+        <v>169</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J76" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>167</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>496</v>
       </c>
       <c r="C77" t="s">
-        <v>430</v>
+        <v>497</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -4599,32 +4587,32 @@
         <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>169</v>
+        <v>498</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J77" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C78" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -4633,169 +4621,170 @@
         <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J78" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="C79" t="s">
-        <v>501</v>
+        <v>452</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J79" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>503</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
-        <v>456</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>504</v>
+        <v>172</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
       </c>
       <c r="J80" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" t="s">
-        <v>172</v>
+        <v>20</v>
+      </c>
+      <c r="H81" t="str">
+        <f>IF(D81="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J81" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H82" t="str">
         <f>IF(D82="basic","cost_power_law_flow")</f>
         <v>cost_power_law_flow</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J82" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D83" t="s">
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -4808,23 +4797,23 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J83" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
@@ -4843,29 +4832,29 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -4873,34 +4862,33 @@
       <c r="G85" t="s">
         <v>12</v>
       </c>
-      <c r="H85" t="str">
-        <f>IF(D85="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+      <c r="H85" t="s">
+        <v>183</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>single-input, single-output</v>
       </c>
       <c r="J85" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>siso_methods</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C86" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -4909,32 +4897,32 @@
         <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, single-output</v>
       </c>
       <c r="J86" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>siso_methods</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -4943,29 +4931,29 @@
         <v>12</v>
       </c>
       <c r="H87" t="s">
-        <v>186</v>
+        <v>460</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, single-output</v>
+        <f t="shared" si="5"/>
+        <v>single-input, double-output</v>
       </c>
       <c r="J87" t="str">
-        <f t="shared" si="8"/>
-        <v>siso_methods</v>
+        <f t="shared" si="6"/>
+        <v>sido_methods</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C88" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -4976,27 +4964,28 @@
       <c r="G88" t="s">
         <v>12</v>
       </c>
-      <c r="H88" t="s">
-        <v>460</v>
+      <c r="H88" t="str">
+        <f>IF(D88="basic","cost_power_law_flow")</f>
+        <v>cost_power_law_flow</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J88" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
@@ -5015,120 +5004,85 @@
         <v>cost_power_law_flow</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>single-input, double-output</v>
       </c>
       <c r="J89" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>sido_methods</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" t="str">
-        <f>IF(D90="basic","cost_power_law_flow")</f>
-        <v>cost_power_law_flow</v>
+        <v>30</v>
+      </c>
+      <c r="H90" t="s">
+        <v>64</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="7"/>
-        <v>single-input, double-output</v>
+        <f t="shared" si="5"/>
+        <v>pass-through</v>
       </c>
       <c r="J90" t="str">
-        <f t="shared" si="8"/>
-        <v>sido_methods</v>
+        <f t="shared" si="6"/>
+        <v>pt_methods</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C91" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H91" t="s">
-        <v>65</v>
+        <v>197</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>pass-through</v>
       </c>
       <c r="J91" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>pt_methods</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>195</v>
-      </c>
-      <c r="B92" t="s">
-        <v>196</v>
-      </c>
-      <c r="C92" t="s">
-        <v>439</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>27</v>
-      </c>
-      <c r="F92" t="b">
-        <v>1</v>
-      </c>
-      <c r="G92" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" t="s">
-        <v>197</v>
-      </c>
-      <c r="I92" t="str">
-        <f t="shared" si="7"/>
-        <v>pass-through</v>
-      </c>
-      <c r="J92" t="str">
-        <f t="shared" si="8"/>
-        <v>pt_methods</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J92">
-    <sortCondition ref="B2:B92"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J91">
+    <sortCondition ref="B2:B91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6189,7 +6143,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="0"/>
@@ -6629,7 +6583,7 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>383</v>
@@ -6637,7 +6591,7 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>421</v>
@@ -6645,7 +6599,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>445</v>
@@ -6661,7 +6615,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>374</v>
@@ -6669,7 +6623,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>375</v>
@@ -6677,7 +6631,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>384</v>
@@ -6693,7 +6647,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>427</v>
@@ -6701,7 +6655,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>386</v>
@@ -6709,7 +6663,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>444</v>
@@ -6717,7 +6671,7 @@
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>388</v>
@@ -6725,7 +6679,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
         <v>387</v>
@@ -6733,7 +6687,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>432</v>
@@ -6741,7 +6695,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>406</v>
@@ -6749,7 +6703,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>434</v>
@@ -6757,7 +6711,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>415</v>
@@ -6765,7 +6719,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>448</v>
@@ -6773,7 +6727,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>449</v>
@@ -6781,7 +6735,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
         <v>377</v>
@@ -6789,7 +6743,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
         <v>389</v>
@@ -6797,7 +6751,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
         <v>378</v>
@@ -6805,7 +6759,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
         <v>390</v>
@@ -6813,7 +6767,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>379</v>
@@ -6821,7 +6775,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
         <v>391</v>
@@ -6829,7 +6783,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
         <v>380</v>
@@ -6837,7 +6791,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
         <v>429</v>
@@ -6845,7 +6799,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
         <v>394</v>
@@ -6853,7 +6807,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
         <v>381</v>
@@ -6861,7 +6815,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>395</v>
@@ -6869,7 +6823,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
         <v>436</v>
@@ -6877,7 +6831,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
         <v>392</v>
@@ -6885,7 +6839,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
         <v>393</v>
@@ -6893,7 +6847,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
         <v>437</v>
@@ -6901,7 +6855,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
         <v>422</v>
@@ -6909,7 +6863,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>428</v>
@@ -6917,7 +6871,7 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
         <v>450</v>
@@ -6933,7 +6887,7 @@
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
         <v>441</v>
@@ -6941,7 +6895,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
         <v>440</v>
@@ -6949,7 +6903,7 @@
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
         <v>426</v>
@@ -6957,7 +6911,7 @@
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
         <v>396</v>
@@ -6965,7 +6919,7 @@
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
         <v>397</v>
@@ -6973,7 +6927,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>399</v>
@@ -6981,7 +6935,7 @@
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
         <v>400</v>
@@ -6989,7 +6943,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
         <v>401</v>
@@ -6997,7 +6951,7 @@
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
         <v>385</v>
@@ -7005,7 +6959,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
         <v>402</v>
